--- a/Crazyflie_charging_deck_components.xlsx
+++ b/Crazyflie_charging_deck_components.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nell.brunner/Desktop/FENCE/KiCad/crazyflie-charging-deck/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F48344-FBFA-5E42-9541-66CE97FD1869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBA156F-5054-224D-BF00-9A1605924DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EF112799-44FD-694D-A537-BC85F1608AD9}"/>
   </bookViews>
@@ -68,18 +68,12 @@
     <t>Buck Boost</t>
   </si>
   <si>
-    <t>OW</t>
-  </si>
-  <si>
     <t>MAX40203AUK+T</t>
   </si>
   <si>
     <t>Ideal diode</t>
   </si>
   <si>
-    <t>https://jlcpcb.com/partdetail/2745548-MAX40203AUKT/C2653639?jlc_vid=QFFbVQdQEQBdAgdSR1VWU1VUQwRdBgIEQwNfBlQCFQcxVlNeQFJeVVNRQFVbVDtW</t>
-  </si>
-  <si>
     <t>WS2812B-V5/W</t>
   </si>
   <si>
@@ -134,13 +128,19 @@
     <t>R 100k 0603</t>
   </si>
   <si>
-    <t>https://jlcpcb.com/partdetail/26546-0603WAF1003T5E/C25803?jlc_vid=R1laUF1VFVQKAlNRElEPXlJXQFJWX1ICE1NZBV0CQ1AxVlNeQFJfVlxWQVVaVTtW</t>
-  </si>
-  <si>
     <t>R 15k 0603</t>
   </si>
   <si>
     <t>https://jlcpcb.com/partdetail/23536-0603WAF1502T5E/C22809</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/2745548-MAX40203AUKT/C2653639</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/26546-0603WAF1003T5E/C25803</t>
+  </si>
+  <si>
+    <t>1-Wire chip</t>
   </si>
 </sst>
 </file>
@@ -566,7 +566,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -577,128 +577,128 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">

--- a/Crazyflie_charging_deck_components.xlsx
+++ b/Crazyflie_charging_deck_components.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nell.brunner/Desktop/FENCE/KiCad/crazyflie-charging-deck/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBA156F-5054-224D-BF00-9A1605924DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4C8245-1F83-2B4E-BC38-650EE40135BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EF112799-44FD-694D-A537-BC85F1608AD9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>Component</t>
   </si>
@@ -62,18 +62,9 @@
     <t>https://jlcpcb.com/partdetail/STMicroelectronics-STBB1APUR/C967636</t>
   </si>
   <si>
-    <t>Use</t>
-  </si>
-  <si>
     <t>Buck Boost</t>
   </si>
   <si>
-    <t>MAX40203AUK+T</t>
-  </si>
-  <si>
-    <t>Ideal diode</t>
-  </si>
-  <si>
     <t>WS2812B-V5/W</t>
   </si>
   <si>
@@ -89,9 +80,6 @@
     <t>https://jlcpcb.com/partdetail/hanxia-HX_PM2_0_1x10P_TPYQ/C42379209</t>
   </si>
   <si>
-    <t>Header 2.0-1x10P smd</t>
-  </si>
-  <si>
     <t>Capacitor</t>
   </si>
   <si>
@@ -134,13 +122,31 @@
     <t>https://jlcpcb.com/partdetail/23536-0603WAF1502T5E/C22809</t>
   </si>
   <si>
-    <t>https://jlcpcb.com/partdetail/2745548-MAX40203AUKT/C2653639</t>
-  </si>
-  <si>
     <t>https://jlcpcb.com/partdetail/26546-0603WAF1003T5E/C25803</t>
   </si>
   <si>
     <t>1-Wire chip</t>
+  </si>
+  <si>
+    <t>MB14F</t>
+  </si>
+  <si>
+    <t>Full bridge rectifier</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/GOODWORK-MB14F/C2943867</t>
+  </si>
+  <si>
+    <t>R 11k 0603</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/26693-0603WAF1102T5E/C25950</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
 </sst>
 </file>
@@ -523,10 +529,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA30D46-0A95-024F-B99A-F6A2D1AEDD8E}">
-  <dimension ref="B2:E14"/>
+  <dimension ref="B2:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.33203125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -538,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -552,10 +558,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
@@ -566,7 +572,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -577,16 +583,16 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -594,132 +600,147 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D6">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D14">
-        <f>SUM(D3:D13)</f>
-        <v>38</v>
+      <c r="E14" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <f>SUM(D3:D14)</f>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{37D2B381-4FA0-3A42-B9D0-A1560EF96825}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{DBA00E4F-101D-494A-AAC9-5BA31B19AFD3}"/>
-    <hyperlink ref="E5" r:id="rId3" xr:uid="{79151F69-71D5-B243-81BB-A0F034B459E9}"/>
-    <hyperlink ref="E6" r:id="rId4" xr:uid="{8305C46E-66F9-354D-8FA9-92B93DCF6091}"/>
-    <hyperlink ref="E7" r:id="rId5" xr:uid="{2803F78D-8788-6042-9B18-82B5BDE06E71}"/>
-    <hyperlink ref="E13" r:id="rId6" xr:uid="{16E68205-108D-0B44-8A9F-ED06EB4FA13A}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{51573662-2A6F-E046-970A-918F36CE5E55}"/>
-    <hyperlink ref="E11" r:id="rId8" xr:uid="{A454B135-EE0A-1740-9CA6-268FBA57DC81}"/>
-    <hyperlink ref="E12" r:id="rId9" xr:uid="{538EB866-3432-2448-A5F2-DE974F26736E}"/>
-    <hyperlink ref="E10" r:id="rId10" xr:uid="{74A17EF0-2CBF-314E-8323-63AB514ECB1A}"/>
-    <hyperlink ref="E9" r:id="rId11" xr:uid="{25322290-611E-A74F-893F-D29BDEC22FA7}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{8305C46E-66F9-354D-8FA9-92B93DCF6091}"/>
+    <hyperlink ref="E6" r:id="rId4" xr:uid="{2803F78D-8788-6042-9B18-82B5BDE06E71}"/>
+    <hyperlink ref="E13" r:id="rId5" xr:uid="{16E68205-108D-0B44-8A9F-ED06EB4FA13A}"/>
+    <hyperlink ref="E7" r:id="rId6" xr:uid="{51573662-2A6F-E046-970A-918F36CE5E55}"/>
+    <hyperlink ref="E11" r:id="rId7" xr:uid="{A454B135-EE0A-1740-9CA6-268FBA57DC81}"/>
+    <hyperlink ref="E12" r:id="rId8" xr:uid="{538EB866-3432-2448-A5F2-DE974F26736E}"/>
+    <hyperlink ref="E10" r:id="rId9" xr:uid="{74A17EF0-2CBF-314E-8323-63AB514ECB1A}"/>
+    <hyperlink ref="E8" r:id="rId10" xr:uid="{25322290-611E-A74F-893F-D29BDEC22FA7}"/>
+    <hyperlink ref="E14" r:id="rId11" xr:uid="{C35541BE-D6B9-4443-9637-05977E770493}"/>
+    <hyperlink ref="E9" r:id="rId12" xr:uid="{54F49863-EDE9-0548-BF45-BDCA63861B85}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
